--- a/回後買上漲圖表_20260617/回後買上漲_嚴格版(1+2+3)_20260617.xlsx
+++ b/回後買上漲圖表_20260617/回後買上漲_嚴格版(1+2+3)_20260617.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -603,28 +603,28 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>6177.TW</t>
+          <t>5905.TWO</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>南仁湖</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>48.25</v>
+        <v>8.9</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>47.45</v>
+        <v>8.51</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2948</v>
+        <v>2352</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>751</v>
+        <v>713</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
@@ -637,258 +637,6 @@
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5905.TWO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>南仁湖</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>2352</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>713</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2439.TW</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>美律</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>4749</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>1899</v>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2520.TW</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>冠德</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>4808</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2185</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2495.TW</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>普安</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>20074</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>11296</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>6269.TW</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>21347</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>12736</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>3653.TW</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>3990</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>3950</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1549</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>1007</v>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -898,12 +646,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
